--- a/results/Int All Data -0.7/Rando_10_permute.xlsx
+++ b/results/Int All Data -0.7/Rando_10_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.861689109096646</v>
+        <v>0.8669888057898343</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7783010554622232</v>
+        <v>0.8740153899070181</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7757217394517737</v>
+        <v>0.8731899661444786</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7741334294136543</v>
+        <v>0.8619577360292676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8060136900244181</v>
+        <v>0.8585014738948631</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8088346281435748</v>
+        <v>0.8594544599177347</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.807870626995159</v>
+        <v>0.8624790001961402</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.798848528521358</v>
+        <v>0.8554303858278685</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7924057460580063</v>
+        <v>0.8895452956175435</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7940455784575413</v>
+        <v>0.8904982816404151</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.798962588369733</v>
+        <v>0.8920485717290763</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8044904047596713</v>
+        <v>0.8985293741418863</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8070317008206624</v>
+        <v>0.89884703614951</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8070317008206624</v>
+        <v>0.897182686212474</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8047050220444641</v>
+        <v>0.8900285398349579</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8071322582570802</v>
+        <v>0.8891515937110028</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8021392084459719</v>
+        <v>0.8444127729974502</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8052287734977501</v>
+        <v>0.840003524840174</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7828563428646149</v>
+        <v>0.8387708967591369</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7824871584955755</v>
+        <v>0.8414397550804602</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7800489071574154</v>
+        <v>0.8385807970118451</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7804315939384119</v>
+        <v>0.8378424282737664</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7640272293903447</v>
+        <v>0.8313616258609564</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7631257657288886</v>
+        <v>0.8318828900278292</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7672198391649541</v>
+        <v>0.8337128221746558</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7928093971101996</v>
+        <v>0.8324801940936186</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7928093971101996</v>
+        <v>0.8318828900278292</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7924917351025758</v>
+        <v>0.8318828900278292</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6993076815932278</v>
+        <v>0.8319969498762042</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6989519996361455</v>
+        <v>0.8339544442833631</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6986343376285217</v>
+        <v>0.835708336531273</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7119356347128534</v>
+        <v>0.8365472627057697</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.71155543521827</v>
+        <v>0.8329254183615746</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7098775828692767</v>
+        <v>0.8220573980425767</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7012491863020163</v>
+        <v>0.8261845168552741</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7006138622867685</v>
+        <v>0.8244686445568224</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6977573915045667</v>
+        <v>0.8255872127894845</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6969699876914854</v>
+        <v>0.8256632526884012</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6973256696485678</v>
+        <v>0.8268958807694384</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6976433316561916</v>
+        <v>0.8243680871204047</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6957753795599066</v>
+        <v>0.8243680871204047</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7098665677437328</v>
+        <v>0.821878313420829</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7067009627930378</v>
+        <v>0.8266947658966028</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7189512037044933</v>
+        <v>0.8066575418787967</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6578865456282033</v>
+        <v>0.8030491999465589</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6635394369920605</v>
+        <v>0.8030491999465589</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6557634690112539</v>
+        <v>0.8005839437844844</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6587499893402011</v>
+        <v>0.8127201248475648</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.578878248040729</v>
+        <v>0.8028861050231815</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5778112021694823</v>
+        <v>0.8071677909201254</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5908353444820618</v>
+        <v>0.8017810392024765</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5862224941655367</v>
+        <v>0.8024163632177242</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5862224941655367</v>
+        <v>0.8147401567416832</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5817752260588023</v>
+        <v>0.8141048327264355</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5402780501948611</v>
+        <v>0.8150578187493072</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5325891372385151</v>
+        <v>0.7868999599191561</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5340253674788012</v>
+        <v>0.7872176219267799</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.534660691494049</v>
+        <v>0.7867723976588239</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5568074897168473</v>
+        <v>0.7839894794891256</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5467698677332151</v>
+        <v>0.7794796738954317</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5465552504484222</v>
+        <v>0.7811060038830094</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5487408645523311</v>
+        <v>0.7832916179869183</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5529980329117739</v>
+        <v>0.7844862261184972</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5609776030518294</v>
+        <v>0.7842446040097899</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5609776030518294</v>
+        <v>0.7988055339990733</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5609776030518294</v>
+        <v>0.7872826467001526</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5609776030518294</v>
+        <v>0.8060762275113775</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5634293568019466</v>
+        <v>0.8033068117536364</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5271153304964055</v>
+        <v>0.8048951217917559</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5258066625164516</v>
+        <v>0.7746301760430259</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5194534223639738</v>
+        <v>0.7467409441454963</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5216770564173411</v>
+        <v>0.7339989311774956</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5213593944097172</v>
+        <v>0.7355627236781139</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5204064083868455</v>
+        <v>0.7429314873404229</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5213974143591755</v>
+        <v>0.7225385813655345</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5146884922496155</v>
+        <v>0.7265786451537711</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5159971602295694</v>
+        <v>0.7255115992825245</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5130621622620377</v>
+        <v>0.755714007544295</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5131001822114961</v>
+        <v>0.7592843295270745</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5146504723001571</v>
+        <v>0.7592843295270745</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5057179161372299</v>
+        <v>0.7585729656129101</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5044472681067345</v>
+        <v>0.7570987154231656</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5054002541296061</v>
+        <v>0.7562597892486689</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5044472681067345</v>
+        <v>0.7379384375293144</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5022236340533672</v>
+        <v>0.741213127755558</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5022236340533672</v>
+        <v>0.7405127789669376</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5013466879294122</v>
+        <v>0.7174375122587687</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5020200318941184</v>
+        <v>0.7174375122587687</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5014607477777873</v>
+        <v>0.7056730028511409</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.4999864975880429</v>
+        <v>0.7065879689245542</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5041921435860701</v>
+        <v>0.7310209386876793</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5013196831054979</v>
+        <v>0.7151758582559432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5042056459980272</v>
+        <v>0.7094199221692549</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5045233080056511</v>
+        <v>0.6876693131394103</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5048029500638167</v>
+        <v>0.619599035217133</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5073062261753494</v>
+        <v>0.5515863202089889</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5082592121982211</v>
+        <v>0.5347502338049228</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5082592121982211</v>
+        <v>0.5394771439698228</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5060355781448539</v>
+        <v>0.5517764199562806</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5015883100381194</v>
+        <v>0.5578745355880941</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5022236340533672</v>
+        <v>0.5699837118272602</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.502858958068615</v>
+        <v>0.5702633538854257</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5047649301143583</v>
+        <v>0.5849898660844995</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5060355781448539</v>
+        <v>0.5840749000110862</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5060355781448539</v>
+        <v>0.5949379457572579</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5073062261753494</v>
+        <v>0.5902625579537735</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5133798242696617</v>
+        <v>0.5845446418165434</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5165184243964421</v>
+        <v>0.5815201015381379</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5165184243964421</v>
+        <v>0.5815201015381379</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5248156565441217</v>
+        <v>0.5767931913732379</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5244979945364977</v>
+        <v>0.574265397724204</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5089325561629272</v>
+        <v>0.5430474659526023</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5089325561629272</v>
+        <v>0.5350678958125468</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5089325561629272</v>
+        <v>0.5341149097896751</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5089325561629272</v>
+        <v>0.5349023136027562</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5092502181705511</v>
+        <v>0.5310903695112695</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5114738522239183</v>
+        <v>0.5300613435894812</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5190977404068916</v>
+        <v>0.544342631520599</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5184624163916438</v>
+        <v>0.5485482775186262</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5238246505717916</v>
+        <v>0.5446983134776812</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5260482846251588</v>
+        <v>0.5450159754853051</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5225920224907544</v>
+        <v>0.5405687073785707</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5232653664554605</v>
+        <v>0.5472911319000878</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5178270923763961</v>
+        <v>0.5466938278342984</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5120711562897078</v>
+        <v>0.5466938278342984</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5009529860228716</v>
+        <v>0.520686050445011</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5003176620076238</v>
+        <v>0.5327572067347188</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5009529860228716</v>
+        <v>0.5410544388823982</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5</v>
+        <v>0.5350188607375443</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5003176620076238</v>
+        <v>0.5398463283388623</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5003176620076238</v>
+        <v>0.5334550682369261</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5003176620076238</v>
+        <v>0.5295020594731501</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5003176620076238</v>
+        <v>0.5245360144859561</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5006353240152478</v>
+        <v>0.53079971232756</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5</v>
+        <v>0.5241643428305035</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5</v>
+        <v>0.5241643428305035</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5</v>
+        <v>0.5241643428305035</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.5423666601286566</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.5227501428413054</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.5142738260718783</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4997203579418344</v>
+        <v>0.513358859998465</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.5109941612728084</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.4961951624411224</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.4955843559633758</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.4972646955987822</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4995167557825856</v>
+        <v>0.4204821640244579</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4995167557825856</v>
+        <v>0.4226347327517347</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4995167557825856</v>
+        <v>0.4445253404739773</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4995167557825856</v>
+        <v>0.4753644940575175</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.49923711372442</v>
+        <v>0.4745255678830208</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4983981875499234</v>
+        <v>0.498677829608089</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4994787358331272</v>
+        <v>0.4983981875499234</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4995167557825856</v>
+        <v>0.4997583778912928</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.5003176620076238</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5000760398989167</v>
+        <v>0.5003176620076238</v>
       </c>
     </row>
   </sheetData>
